--- a/data/trans_orig/P44C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6944</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6236</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6663</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>30466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39573</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51444</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80557</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73194</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>90659</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122878</t>
+          <t>123719</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31588</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016 (tasa de respuesta: 96,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>24330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>46589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81924</t>
+          <t>80069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39730</t>
+          <t>38922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100829</t>
+          <t>101080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46716</t>
+          <t>46350</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68634</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>130257</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163909</t>
+          <t>164982</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>40924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>34810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023 (tasa de respuesta: 96,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>45631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>63913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86783</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>66802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>86119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95252</t>
+          <t>95536</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113172</t>
+          <t>112747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167571</t>
+          <t>165656</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>194173</t>
+          <t>192336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54565</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133695</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70454</t>
+          <t>68708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50101</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197166</t>
+          <t>193836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237517</t>
+          <t>238234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460709</t>
+          <t>467695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112028</t>
+          <t>110992</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334217</t>
+          <t>337647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616642</t>
+          <t>603929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>121455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>171731</t>
+          <t>167236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66805</t>
+          <t>67950</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>39535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58598</t>
+          <t>57461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67673</t>
+          <t>68047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89331</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56735</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204690</t>
+          <t>206134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>109523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137542</t>
+          <t>136271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134961</t>
+          <t>136710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330374</t>
+          <t>329351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>361152</t>
+          <t>359050</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>640646</t>
+          <t>646045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,47 +7694,47 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>47,47%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>85,41%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>235084</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>219764</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>250484</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>51,08%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>47,75%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>84,7%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>235084</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>218943</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>250191</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>51,08%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>597325</t>
+          <t>597335</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>953049</t>
+          <t>950542</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49060</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172475</t>
+          <t>170157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99064</t>
+          <t>99139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108646</t>
+          <t>104427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255218</t>
+          <t>254079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Estudios-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>31036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48597</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27846</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36413</t>
+          <t>36080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48706</t>
+          <t>49416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81210</t>
+          <t>79875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34122</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55065</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123719</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>48974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24739</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>38782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59444</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80069</t>
+          <t>80217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49229</t>
+          <t>49564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>66298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27794</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19565</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>39415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49827</t>
+          <t>49732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75649</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101080</t>
+          <t>101572</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>69480</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>130257</t>
+          <t>129216</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164982</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34810</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61515</t>
+          <t>60071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -5741,32 +5741,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,32 +5776,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,32 +5811,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5854,32 +5854,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45631</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,32 +5889,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>41860</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47174</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,32 +5924,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>75081</t>
+          <t>78334</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63913</t>
+          <t>67052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>90157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -5967,32 +5967,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76351</t>
+          <t>82734</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66802</t>
+          <t>72529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86119</t>
+          <t>93490</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,32 +6002,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104063</t>
+          <t>116204</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95536</t>
+          <t>106270</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112747</t>
+          <t>125483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,32 +6037,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>180414</t>
+          <t>198937</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165656</t>
+          <t>185456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>192336</t>
+          <t>212273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -6080,32 +6080,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>25076</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,32 +6115,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,32 +6150,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>47677</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -6193,17 +6193,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>147233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>147233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>147233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,17 +6228,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>183305</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>183305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>183305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>304250</t>
+          <t>330538</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304250</t>
+          <t>330538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>304250</t>
+          <t>330538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6310,32 +6310,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6345,67 +6345,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>15771</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>9722</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>24355</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>4,74%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>14599</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>4987</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>25481</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64672</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132015</t>
+          <t>79868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>64922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49149</t>
+          <t>54417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>75833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,32 +6493,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>124706</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>115481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193836</t>
+          <t>149337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -6536,32 +6536,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>370379</t>
+          <t>138310</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238234</t>
+          <t>122694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467695</t>
+          <t>152717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,32 +6571,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100483</t>
+          <t>112401</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>97674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110992</t>
+          <t>122704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>470862</t>
+          <t>250711</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337647</t>
+          <t>230995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>603929</t>
+          <t>270979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -6649,32 +6649,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>65475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121455</t>
+          <t>79135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,32 +6684,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47817</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>61598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,32 +6719,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>107018</t>
+          <t>116608</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>100706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167236</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -6762,17 +6762,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>503097</t>
+          <t>279817</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>503097</t>
+          <t>279817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>503097</t>
+          <t>279817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>234456</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>234456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>234456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>717186</t>
+          <t>514273</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717186</t>
+          <t>514273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>717186</t>
+          <t>514273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6879,32 +6879,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,32 +6914,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -6992,32 +6992,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40790</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7027,32 +7027,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>33776</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7062,32 +7062,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56306</t>
+          <t>58987</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>49206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67950</t>
+          <t>71075</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -7105,32 +7105,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57461</t>
+          <t>60922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78858</t>
+          <t>86242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68047</t>
+          <t>73954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>98421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28739</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>39005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,32 +7288,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>40496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115228</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115228</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115228</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>79917</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79917</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79917</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>195144</t>
+          <t>211542</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195144</t>
+          <t>211542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195144</t>
+          <t>211542</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,32 +7518,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46666</t>
+          <t>47107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>132977</t>
+          <t>134826</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56701</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206134</t>
+          <t>154552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7596,32 +7596,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>123117</t>
+          <t>133678</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109523</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>256093</t>
+          <t>268503</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136710</t>
+          <t>246473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329351</t>
+          <t>291793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -7674,32 +7674,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>495051</t>
+          <t>272362</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359050</t>
+          <t>252374</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646045</t>
+          <t>293178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7709,32 +7709,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>235084</t>
+          <t>263528</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>246515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>250484</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7744,32 +7744,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>730134</t>
+          <t>535890</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>597335</t>
+          <t>512453</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>950542</t>
+          <t>565413</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -7787,32 +7787,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>104184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170157</t>
+          <t>139857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,32 +7822,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>107921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104427</t>
+          <t>193528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254079</t>
+          <t>239625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -7900,17 +7900,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>756377</t>
+          <t>547581</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>756377</t>
+          <t>547581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>756377</t>
+          <t>547581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1216580</t>
+          <t>1056353</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1216580</t>
+          <t>1056353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1216580</t>
+          <t>1056353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
